--- a/output/pdf_financials_xlsx/LET.H.xlsx
+++ b/output/pdf_financials_xlsx/LET.H.xlsx
@@ -1266,10 +1266,10 @@
         <v>-0.666851</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.990873</v>
+        <v>-1.990873</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.5311439999999999</v>
+        <v>-0.5311439999999999</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.730108</v>
@@ -1554,10 +1554,10 @@
         <v>-0.611851</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.990873</v>
+        <v>-1.990873</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.5311439999999999</v>
+        <v>-0.5311439999999999</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.730108</v>
@@ -1725,10 +1725,10 @@
         <v>-0.611851</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.990873</v>
+        <v>-1.990873</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5311439999999999</v>
+        <v>-0.5311439999999999</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.730108</v>
@@ -1896,10 +1896,10 @@
         <v>20.395033</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>39.81746</v>
+        <v>-39.81746</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.547571</v>
+        <v>-0.547571</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>1.622462</v>
@@ -1959,10 +1959,10 @@
         <v>-0.666851</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.990873</v>
+        <v>-1.990873</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5311439999999999</v>
+        <v>-0.5311439999999999</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.730108</v>
@@ -2073,10 +2073,10 @@
         <v>-0.666851</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.990873</v>
+        <v>-1.990873</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.532392</v>
+        <v>-0.529896</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.730108</v>
@@ -2217,10 +2217,10 @@
         <v>-8.247719505556713</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -5845,13 +5845,13 @@
         <v>0.018336</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.285643</v>
+        <v>0.018336</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.471371</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.471371</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -5866,16 +5866,16 @@
         <v>0</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.050523</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.083123</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.222617</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.097763</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -7313,10 +7313,10 @@
         <v>-0.298951</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.257165</v>
+        <v>0.250665</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.5822040000000001</v>
+        <v>0.572204</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0.173609</v>
@@ -10044,7 +10044,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -10810,7 +10814,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11376,7 +11384,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -12716,7 +12728,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -13672,7 +13688,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -14928,7 +14948,11 @@
           <t>Reserves 471,371</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -22662,7 +22686,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -35236,7 +35264,7 @@
         </is>
       </c>
       <c r="I284" s="5" t="n">
-        <v>0.5311439999999999</v>
+        <v>-0.5311439999999999</v>
       </c>
       <c r="J284" s="5" t="n">
         <v>-0.730108</v>
@@ -40551,10 +40579,10 @@
         </is>
       </c>
       <c r="H340" s="5" t="n">
-        <v>1.990873</v>
+        <v>-1.990873</v>
       </c>
       <c r="I340" s="5" t="n">
-        <v>0.5311439999999999</v>
+        <v>-0.5311439999999999</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LET.H.xlsx
+++ b/output/pdf_financials_xlsx/LET.H.xlsx
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>2.3e-05</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1065,16 +1065,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000648</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00068</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000443</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000749</v>
       </c>
     </row>
     <row r="13">
@@ -1965,7 +1965,7 @@
         <v>-0.5311439999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.730108</v>
+        <v>-0.730131</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.38992</v>
@@ -1986,16 +1986,16 @@
         <v>-0.476721</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.149068</v>
+        <v>-1.149716</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.580881</v>
+        <v>-0.581561</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.011292</v>
+        <v>-0.011735</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.011292</v>
+        <v>-0.012041</v>
       </c>
     </row>
     <row r="28">
@@ -2079,7 +2079,7 @@
         <v>-0.529896</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.730108</v>
+        <v>-0.730131</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.38992</v>
@@ -2100,16 +2100,16 @@
         <v>-0.476721</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.149068</v>
+        <v>-1.149716</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.580881</v>
+        <v>-0.581561</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.011292</v>
+        <v>-0.011735</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.011292</v>
+        <v>-0.012041</v>
       </c>
     </row>
     <row r="30">
@@ -2362,49 +2362,49 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.055136</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.055136</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.034739</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000523</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.020741</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.070839</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.011933</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.116154</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.045424</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.035176</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.06950199999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.183649</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.115155</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.007963</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.001164</v>
       </c>
     </row>
     <row r="35">
@@ -2476,49 +2476,49 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.055136</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.055136</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.034739</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000523</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.020741</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.070839</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.011933</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.116154</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.045424</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.035176</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.06950199999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.183649</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.115155</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.007963</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.001164</v>
       </c>
     </row>
     <row r="37">
@@ -3160,49 +3160,49 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.128456</v>
+        <v>0.07332</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.128456</v>
+        <v>0.07332</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.038439</v>
+        <v>0.0037</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.001759</v>
+        <v>0.001236</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.022112</v>
+        <v>0.001371</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.070839</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.011933</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.116409</v>
+        <v>0.000255</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.045679</v>
+        <v>0.000255</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.040431</v>
+        <v>0.005255</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.106439</v>
+        <v>0.036937</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.192654</v>
+        <v>0.009005000000000001</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.545876</v>
+        <v>0.430721</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.406429</v>
+        <v>0.398466</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.393991</v>
+        <v>0.392827</v>
       </c>
     </row>
     <row r="49">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -27608,7 +27608,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -37126,7 +37126,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
